--- a/backend/data/financials_by_company/0436.HK.xlsx
+++ b/backend/data/financials_by_company/0436.HK.xlsx
@@ -4378,7 +4378,7 @@
         <v>-9569000</v>
       </c>
       <c r="BR2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS2" t="n">
         <v>0.21</v>
@@ -4573,7 +4573,7 @@
         <v>0</v>
       </c>
       <c r="DU2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DV2" t="n">
         <v>0.0038199984</v>
